--- a/data_voor_swing/uploadfiles/ggw7_type.xlsx
+++ b/data_voor_swing/uploadfiles/ggw7_type.xlsx
@@ -1,21 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29530"/>
-  <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\01_interprovinciaal\07_redegeo\10_implementatie_in_pinc\05_wijken\outputbestanden_voor_pinc\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{09A90951-5016-405E-9B02-C4BE04661C01}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
+  <workbookPr defaultThemeVersion="124226"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
@@ -61,10 +55,10 @@
     <t>11013W01</t>
   </si>
   <si>
-    <t>11016A0W</t>
-  </si>
-  <si>
-    <t>11018A0W</t>
+    <t>11016W01</t>
+  </si>
+  <si>
+    <t>11018W01</t>
   </si>
   <si>
     <t>11021W01</t>
@@ -85,19 +79,19 @@
     <t>11029W01</t>
   </si>
   <si>
-    <t>11030A0W</t>
-  </si>
-  <si>
-    <t>11035A0W</t>
-  </si>
-  <si>
-    <t>11037A0W</t>
-  </si>
-  <si>
-    <t>11038A0W</t>
-  </si>
-  <si>
-    <t>11039A0W</t>
+    <t>11030W01</t>
+  </si>
+  <si>
+    <t>11035W01</t>
+  </si>
+  <si>
+    <t>11037W01</t>
+  </si>
+  <si>
+    <t>11038W01</t>
+  </si>
+  <si>
+    <t>11039W01</t>
   </si>
   <si>
     <t>11040W01</t>
@@ -112,10 +106,10 @@
     <t>11052W01</t>
   </si>
   <si>
-    <t>11053A0W</t>
-  </si>
-  <si>
-    <t>11054A0W</t>
+    <t>11053W01</t>
+  </si>
+  <si>
+    <t>11054W01</t>
   </si>
   <si>
     <t>11055W01</t>
@@ -172,7 +166,7 @@
     <t>13004W01</t>
   </si>
   <si>
-    <t>13006A0W</t>
+    <t>13006W01</t>
   </si>
   <si>
     <t>13008W01</t>
@@ -193,7 +187,7 @@
     <t>13014W01</t>
   </si>
   <si>
-    <t>13016A0W</t>
+    <t>13016W01</t>
   </si>
   <si>
     <t>13017W01</t>
@@ -205,7 +199,7 @@
     <t>13021W01</t>
   </si>
   <si>
-    <t>13023A0W</t>
+    <t>13023W01</t>
   </si>
   <si>
     <t>13025W01</t>
@@ -220,16 +214,16 @@
     <t>13035W01</t>
   </si>
   <si>
-    <t>13036A0W</t>
-  </si>
-  <si>
-    <t>13037A0W</t>
+    <t>13036W01</t>
+  </si>
+  <si>
+    <t>13037W01</t>
   </si>
   <si>
     <t>13040W01</t>
   </si>
   <si>
-    <t>13044A0W</t>
+    <t>13044W01</t>
   </si>
   <si>
     <t>13046W01</t>
@@ -499,7 +493,7 @@
     <t>31006W01</t>
   </si>
   <si>
-    <t>31012A0W</t>
+    <t>31012W01</t>
   </si>
   <si>
     <t>31022W01</t>
@@ -721,7 +715,7 @@
     <t>42011A0W</t>
   </si>
   <si>
-    <t>42023A0W</t>
+    <t>42023W01</t>
   </si>
   <si>
     <t>42025A0W</t>
@@ -751,7 +745,7 @@
     <t>43018W01</t>
   </si>
   <si>
-    <t>44013A0W</t>
+    <t>44013W01</t>
   </si>
   <si>
     <t>44019W01</t>
@@ -769,7 +763,7 @@
     <t>44064A0W</t>
   </si>
   <si>
-    <t>44081A0W</t>
+    <t>44081W01</t>
   </si>
   <si>
     <t>44083W01</t>
@@ -778,16 +772,16 @@
     <t>44001A0W</t>
   </si>
   <si>
-    <t>44036A0W</t>
+    <t>44085W01</t>
   </si>
   <si>
     <t>44086W01</t>
   </si>
   <si>
-    <t>44034A0W</t>
-  </si>
-  <si>
-    <t>44040A0W</t>
+    <t>44087W01</t>
+  </si>
+  <si>
+    <t>44088W01</t>
   </si>
   <si>
     <t>45035A0W</t>
@@ -802,7 +796,7 @@
     <t>45060W01</t>
   </si>
   <si>
-    <t>45061A0W</t>
+    <t>45061W01</t>
   </si>
   <si>
     <t>45062A0W</t>
@@ -814,7 +808,7 @@
     <t>45064W01</t>
   </si>
   <si>
-    <t>45065A0W</t>
+    <t>45065W01</t>
   </si>
   <si>
     <t>45017A0W</t>
@@ -910,7 +904,7 @@
     <t>72038W01</t>
   </si>
   <si>
-    <t>72039A0W</t>
+    <t>72039W01</t>
   </si>
   <si>
     <t>72041W01</t>
@@ -955,8 +949,8 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <fonts count="2">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -967,7 +961,10 @@
     <font>
       <b/>
       <sz val="11"/>
+      <color theme="1"/>
       <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="2">
@@ -1012,18 +1009,10 @@
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Standaard" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
 </styleSheet>
 </file>
 
@@ -1311,18 +1300,11 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:E305"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="1" max="1" width="10.140625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="8.42578125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="6.85546875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="16.7109375" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="16.5703125" bestFit="1" customWidth="1"/>
-  </cols>
+  <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:5">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1339,7 +1321,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:5">
       <c r="A2" t="s">
         <v>5</v>
       </c>
@@ -1356,7 +1338,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:5">
       <c r="A3" t="s">
         <v>5</v>
       </c>
@@ -1373,7 +1355,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:5">
       <c r="A4" t="s">
         <v>5</v>
       </c>
@@ -1390,7 +1372,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:5">
       <c r="A5" t="s">
         <v>5</v>
       </c>
@@ -1407,7 +1389,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:5">
       <c r="A6" t="s">
         <v>5</v>
       </c>
@@ -1418,13 +1400,13 @@
         <v>1970</v>
       </c>
       <c r="D6">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E6" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:5">
       <c r="A7" t="s">
         <v>5</v>
       </c>
@@ -1441,7 +1423,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:5">
       <c r="A8" t="s">
         <v>5</v>
       </c>
@@ -1458,7 +1440,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:5">
       <c r="A9" t="s">
         <v>5</v>
       </c>
@@ -1469,13 +1451,13 @@
         <v>1970</v>
       </c>
       <c r="D9">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E9" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:5">
       <c r="A10" t="s">
         <v>5</v>
       </c>
@@ -1486,13 +1468,13 @@
         <v>1970</v>
       </c>
       <c r="D10">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E10" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:5">
       <c r="A11" t="s">
         <v>5</v>
       </c>
@@ -1509,7 +1491,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:5">
       <c r="A12" t="s">
         <v>5</v>
       </c>
@@ -1526,7 +1508,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:5">
       <c r="A13" t="s">
         <v>5</v>
       </c>
@@ -1543,7 +1525,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:5">
       <c r="A14" t="s">
         <v>5</v>
       </c>
@@ -1560,7 +1542,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:5">
       <c r="A15" t="s">
         <v>5</v>
       </c>
@@ -1577,7 +1559,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:5">
       <c r="A16" t="s">
         <v>5</v>
       </c>
@@ -1594,7 +1576,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:5">
       <c r="A17" t="s">
         <v>5</v>
       </c>
@@ -1605,13 +1587,13 @@
         <v>1970</v>
       </c>
       <c r="D17">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E17" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:5">
       <c r="A18" t="s">
         <v>5</v>
       </c>
@@ -1622,13 +1604,13 @@
         <v>1970</v>
       </c>
       <c r="D18">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E18" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:5">
       <c r="A19" t="s">
         <v>5</v>
       </c>
@@ -1639,13 +1621,13 @@
         <v>1970</v>
       </c>
       <c r="D19">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E19" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:5">
       <c r="A20" t="s">
         <v>5</v>
       </c>
@@ -1656,13 +1638,13 @@
         <v>1970</v>
       </c>
       <c r="D20">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E20" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:5">
       <c r="A21" t="s">
         <v>5</v>
       </c>
@@ -1673,13 +1655,13 @@
         <v>1970</v>
       </c>
       <c r="D21">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E21" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:5">
       <c r="A22" t="s">
         <v>5</v>
       </c>
@@ -1696,7 +1678,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="23" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:5">
       <c r="A23" t="s">
         <v>5</v>
       </c>
@@ -1713,7 +1695,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="24" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:5">
       <c r="A24" t="s">
         <v>5</v>
       </c>
@@ -1730,7 +1712,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="25" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:5">
       <c r="A25" t="s">
         <v>5</v>
       </c>
@@ -1747,7 +1729,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="26" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:5">
       <c r="A26" t="s">
         <v>5</v>
       </c>
@@ -1758,13 +1740,13 @@
         <v>1970</v>
       </c>
       <c r="D26">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E26" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="27" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:5">
       <c r="A27" t="s">
         <v>5</v>
       </c>
@@ -1775,13 +1757,13 @@
         <v>1970</v>
       </c>
       <c r="D27">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E27" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="28" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:5">
       <c r="A28" t="s">
         <v>5</v>
       </c>
@@ -1798,7 +1780,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="29" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:5">
       <c r="A29" t="s">
         <v>5</v>
       </c>
@@ -1815,7 +1797,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="30" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:5">
       <c r="A30" t="s">
         <v>5</v>
       </c>
@@ -1832,7 +1814,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="31" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:5">
       <c r="A31" t="s">
         <v>5</v>
       </c>
@@ -1849,7 +1831,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="32" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:5">
       <c r="A32" t="s">
         <v>5</v>
       </c>
@@ -1866,7 +1848,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="33" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:5">
       <c r="A33" t="s">
         <v>5</v>
       </c>
@@ -1883,7 +1865,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="34" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:5">
       <c r="A34" t="s">
         <v>5</v>
       </c>
@@ -1900,7 +1882,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="35" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:5">
       <c r="A35" t="s">
         <v>5</v>
       </c>
@@ -1917,7 +1899,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="36" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:5">
       <c r="A36" t="s">
         <v>5</v>
       </c>
@@ -1934,7 +1916,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="37" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:5">
       <c r="A37" t="s">
         <v>5</v>
       </c>
@@ -1951,7 +1933,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="38" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:5">
       <c r="A38" t="s">
         <v>5</v>
       </c>
@@ -1968,7 +1950,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="39" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:5">
       <c r="A39" t="s">
         <v>5</v>
       </c>
@@ -1985,7 +1967,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="40" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:5">
       <c r="A40" t="s">
         <v>5</v>
       </c>
@@ -2002,7 +1984,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="41" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:5">
       <c r="A41" t="s">
         <v>5</v>
       </c>
@@ -2019,7 +2001,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="42" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:5">
       <c r="A42" t="s">
         <v>5</v>
       </c>
@@ -2036,7 +2018,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="43" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:5">
       <c r="A43" t="s">
         <v>5</v>
       </c>
@@ -2053,7 +2035,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="44" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:5">
       <c r="A44" t="s">
         <v>5</v>
       </c>
@@ -2070,7 +2052,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="45" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:5">
       <c r="A45" t="s">
         <v>5</v>
       </c>
@@ -2087,7 +2069,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="46" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:5">
       <c r="A46" t="s">
         <v>5</v>
       </c>
@@ -2098,13 +2080,13 @@
         <v>1970</v>
       </c>
       <c r="D46">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E46" t="s">
         <v>50</v>
       </c>
     </row>
-    <row r="47" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:5">
       <c r="A47" t="s">
         <v>5</v>
       </c>
@@ -2121,7 +2103,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="48" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:5">
       <c r="A48" t="s">
         <v>5</v>
       </c>
@@ -2138,7 +2120,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="49" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:5">
       <c r="A49" t="s">
         <v>5</v>
       </c>
@@ -2155,7 +2137,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="50" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:5">
       <c r="A50" t="s">
         <v>5</v>
       </c>
@@ -2172,7 +2154,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="51" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:5">
       <c r="A51" t="s">
         <v>5</v>
       </c>
@@ -2189,7 +2171,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="52" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:5">
       <c r="A52" t="s">
         <v>5</v>
       </c>
@@ -2206,7 +2188,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="53" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:5">
       <c r="A53" t="s">
         <v>5</v>
       </c>
@@ -2217,13 +2199,13 @@
         <v>1970</v>
       </c>
       <c r="D53">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E53" t="s">
         <v>57</v>
       </c>
     </row>
-    <row r="54" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:5">
       <c r="A54" t="s">
         <v>5</v>
       </c>
@@ -2240,7 +2222,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="55" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:5">
       <c r="A55" t="s">
         <v>5</v>
       </c>
@@ -2257,7 +2239,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="56" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:5">
       <c r="A56" t="s">
         <v>5</v>
       </c>
@@ -2274,7 +2256,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="57" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:5">
       <c r="A57" t="s">
         <v>5</v>
       </c>
@@ -2285,13 +2267,13 @@
         <v>1970</v>
       </c>
       <c r="D57">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E57" t="s">
         <v>61</v>
       </c>
     </row>
-    <row r="58" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:5">
       <c r="A58" t="s">
         <v>5</v>
       </c>
@@ -2308,7 +2290,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="59" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:5">
       <c r="A59" t="s">
         <v>5</v>
       </c>
@@ -2325,7 +2307,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="60" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:5">
       <c r="A60" t="s">
         <v>5</v>
       </c>
@@ -2342,7 +2324,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="61" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:5">
       <c r="A61" t="s">
         <v>5</v>
       </c>
@@ -2359,7 +2341,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="62" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:5">
       <c r="A62" t="s">
         <v>5</v>
       </c>
@@ -2370,13 +2352,13 @@
         <v>1970</v>
       </c>
       <c r="D62">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E62" t="s">
         <v>66</v>
       </c>
     </row>
-    <row r="63" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:5">
       <c r="A63" t="s">
         <v>5</v>
       </c>
@@ -2387,13 +2369,13 @@
         <v>1970</v>
       </c>
       <c r="D63">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E63" t="s">
         <v>67</v>
       </c>
     </row>
-    <row r="64" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:5">
       <c r="A64" t="s">
         <v>5</v>
       </c>
@@ -2410,7 +2392,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="65" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:5">
       <c r="A65" t="s">
         <v>5</v>
       </c>
@@ -2421,13 +2403,13 @@
         <v>1970</v>
       </c>
       <c r="D65">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E65" t="s">
         <v>69</v>
       </c>
     </row>
-    <row r="66" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:5">
       <c r="A66" t="s">
         <v>5</v>
       </c>
@@ -2444,7 +2426,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="67" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:5">
       <c r="A67" t="s">
         <v>5</v>
       </c>
@@ -2461,7 +2443,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="68" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:5">
       <c r="A68" t="s">
         <v>5</v>
       </c>
@@ -2478,7 +2460,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="69" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:5">
       <c r="A69" t="s">
         <v>5</v>
       </c>
@@ -2495,7 +2477,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="70" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:5">
       <c r="A70" t="s">
         <v>5</v>
       </c>
@@ -2512,7 +2494,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="71" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:5">
       <c r="A71" t="s">
         <v>5</v>
       </c>
@@ -2529,7 +2511,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="72" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:5">
       <c r="A72" t="s">
         <v>5</v>
       </c>
@@ -2546,7 +2528,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="73" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:5">
       <c r="A73" t="s">
         <v>5</v>
       </c>
@@ -2563,7 +2545,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="74" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:5">
       <c r="A74" t="s">
         <v>5</v>
       </c>
@@ -2580,7 +2562,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="75" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:5">
       <c r="A75" t="s">
         <v>5</v>
       </c>
@@ -2597,7 +2579,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="76" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:5">
       <c r="A76" t="s">
         <v>5</v>
       </c>
@@ -2614,7 +2596,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="77" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:5">
       <c r="A77" t="s">
         <v>5</v>
       </c>
@@ -2631,7 +2613,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="78" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:5">
       <c r="A78" t="s">
         <v>5</v>
       </c>
@@ -2648,7 +2630,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="79" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:5">
       <c r="A79" t="s">
         <v>5</v>
       </c>
@@ -2665,7 +2647,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="80" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:5">
       <c r="A80" t="s">
         <v>5</v>
       </c>
@@ -2682,7 +2664,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="81" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:5">
       <c r="A81" t="s">
         <v>5</v>
       </c>
@@ -2699,7 +2681,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="82" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:5">
       <c r="A82" t="s">
         <v>5</v>
       </c>
@@ -2716,7 +2698,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="83" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:5">
       <c r="A83" t="s">
         <v>5</v>
       </c>
@@ -2733,7 +2715,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="84" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:5">
       <c r="A84" t="s">
         <v>5</v>
       </c>
@@ -2750,7 +2732,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="85" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:5">
       <c r="A85" t="s">
         <v>5</v>
       </c>
@@ -2767,7 +2749,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="86" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:5">
       <c r="A86" t="s">
         <v>5</v>
       </c>
@@ -2784,7 +2766,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="87" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:5">
       <c r="A87" t="s">
         <v>5</v>
       </c>
@@ -2801,7 +2783,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="88" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:5">
       <c r="A88" t="s">
         <v>5</v>
       </c>
@@ -2818,7 +2800,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="89" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:5">
       <c r="A89" t="s">
         <v>5</v>
       </c>
@@ -2835,7 +2817,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="90" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:5">
       <c r="A90" t="s">
         <v>5</v>
       </c>
@@ -2852,7 +2834,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="91" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:5">
       <c r="A91" t="s">
         <v>5</v>
       </c>
@@ -2869,7 +2851,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="92" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:5">
       <c r="A92" t="s">
         <v>5</v>
       </c>
@@ -2886,7 +2868,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="93" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:5">
       <c r="A93" t="s">
         <v>5</v>
       </c>
@@ -2903,7 +2885,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="94" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:5">
       <c r="A94" t="s">
         <v>5</v>
       </c>
@@ -2920,7 +2902,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="95" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:5">
       <c r="A95" t="s">
         <v>5</v>
       </c>
@@ -2937,7 +2919,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="96" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:5">
       <c r="A96" t="s">
         <v>5</v>
       </c>
@@ -2954,7 +2936,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="97" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:5">
       <c r="A97" t="s">
         <v>5</v>
       </c>
@@ -2971,7 +2953,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="98" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:5">
       <c r="A98" t="s">
         <v>5</v>
       </c>
@@ -2988,7 +2970,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="99" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:5">
       <c r="A99" t="s">
         <v>5</v>
       </c>
@@ -3005,7 +2987,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="100" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:5">
       <c r="A100" t="s">
         <v>5</v>
       </c>
@@ -3022,7 +3004,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="101" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:5">
       <c r="A101" t="s">
         <v>5</v>
       </c>
@@ -3039,7 +3021,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="102" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:5">
       <c r="A102" t="s">
         <v>5</v>
       </c>
@@ -3056,7 +3038,7 @@
         <v>106</v>
       </c>
     </row>
-    <row r="103" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:5">
       <c r="A103" t="s">
         <v>5</v>
       </c>
@@ -3073,7 +3055,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="104" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:5">
       <c r="A104" t="s">
         <v>5</v>
       </c>
@@ -3090,7 +3072,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="105" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:5">
       <c r="A105" t="s">
         <v>5</v>
       </c>
@@ -3107,7 +3089,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="106" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:5">
       <c r="A106" t="s">
         <v>5</v>
       </c>
@@ -3124,7 +3106,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="107" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:5">
       <c r="A107" t="s">
         <v>5</v>
       </c>
@@ -3141,7 +3123,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="108" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:5">
       <c r="A108" t="s">
         <v>5</v>
       </c>
@@ -3158,7 +3140,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="109" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:5">
       <c r="A109" t="s">
         <v>5</v>
       </c>
@@ -3175,7 +3157,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="110" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:5">
       <c r="A110" t="s">
         <v>5</v>
       </c>
@@ -3192,7 +3174,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="111" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:5">
       <c r="A111" t="s">
         <v>5</v>
       </c>
@@ -3209,7 +3191,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="112" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:5">
       <c r="A112" t="s">
         <v>5</v>
       </c>
@@ -3226,7 +3208,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="113" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:5">
       <c r="A113" t="s">
         <v>5</v>
       </c>
@@ -3243,7 +3225,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="114" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:5">
       <c r="A114" t="s">
         <v>5</v>
       </c>
@@ -3260,7 +3242,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="115" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:5">
       <c r="A115" t="s">
         <v>5</v>
       </c>
@@ -3277,7 +3259,7 @@
         <v>119</v>
       </c>
     </row>
-    <row r="116" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:5">
       <c r="A116" t="s">
         <v>5</v>
       </c>
@@ -3294,7 +3276,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="117" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:5">
       <c r="A117" t="s">
         <v>5</v>
       </c>
@@ -3311,7 +3293,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="118" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:5">
       <c r="A118" t="s">
         <v>5</v>
       </c>
@@ -3328,7 +3310,7 @@
         <v>122</v>
       </c>
     </row>
-    <row r="119" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:5">
       <c r="A119" t="s">
         <v>5</v>
       </c>
@@ -3345,7 +3327,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="120" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:5">
       <c r="A120" t="s">
         <v>5</v>
       </c>
@@ -3362,7 +3344,7 @@
         <v>124</v>
       </c>
     </row>
-    <row r="121" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:5">
       <c r="A121" t="s">
         <v>5</v>
       </c>
@@ -3379,7 +3361,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="122" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:5">
       <c r="A122" t="s">
         <v>5</v>
       </c>
@@ -3396,7 +3378,7 @@
         <v>126</v>
       </c>
     </row>
-    <row r="123" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:5">
       <c r="A123" t="s">
         <v>5</v>
       </c>
@@ -3413,7 +3395,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="124" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:5">
       <c r="A124" t="s">
         <v>5</v>
       </c>
@@ -3430,7 +3412,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="125" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:5">
       <c r="A125" t="s">
         <v>5</v>
       </c>
@@ -3447,7 +3429,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="126" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:5">
       <c r="A126" t="s">
         <v>5</v>
       </c>
@@ -3464,7 +3446,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="127" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:5">
       <c r="A127" t="s">
         <v>5</v>
       </c>
@@ -3481,7 +3463,7 @@
         <v>131</v>
       </c>
     </row>
-    <row r="128" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:5">
       <c r="A128" t="s">
         <v>5</v>
       </c>
@@ -3498,7 +3480,7 @@
         <v>132</v>
       </c>
     </row>
-    <row r="129" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="129" spans="1:5">
       <c r="A129" t="s">
         <v>5</v>
       </c>
@@ -3515,7 +3497,7 @@
         <v>133</v>
       </c>
     </row>
-    <row r="130" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="130" spans="1:5">
       <c r="A130" t="s">
         <v>5</v>
       </c>
@@ -3532,7 +3514,7 @@
         <v>134</v>
       </c>
     </row>
-    <row r="131" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="131" spans="1:5">
       <c r="A131" t="s">
         <v>5</v>
       </c>
@@ -3549,7 +3531,7 @@
         <v>135</v>
       </c>
     </row>
-    <row r="132" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="132" spans="1:5">
       <c r="A132" t="s">
         <v>5</v>
       </c>
@@ -3566,7 +3548,7 @@
         <v>136</v>
       </c>
     </row>
-    <row r="133" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="133" spans="1:5">
       <c r="A133" t="s">
         <v>5</v>
       </c>
@@ -3583,7 +3565,7 @@
         <v>137</v>
       </c>
     </row>
-    <row r="134" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="134" spans="1:5">
       <c r="A134" t="s">
         <v>5</v>
       </c>
@@ -3600,7 +3582,7 @@
         <v>138</v>
       </c>
     </row>
-    <row r="135" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="135" spans="1:5">
       <c r="A135" t="s">
         <v>5</v>
       </c>
@@ -3617,7 +3599,7 @@
         <v>139</v>
       </c>
     </row>
-    <row r="136" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="136" spans="1:5">
       <c r="A136" t="s">
         <v>5</v>
       </c>
@@ -3634,7 +3616,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="137" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="137" spans="1:5">
       <c r="A137" t="s">
         <v>5</v>
       </c>
@@ -3651,7 +3633,7 @@
         <v>141</v>
       </c>
     </row>
-    <row r="138" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="138" spans="1:5">
       <c r="A138" t="s">
         <v>5</v>
       </c>
@@ -3668,7 +3650,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="139" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="139" spans="1:5">
       <c r="A139" t="s">
         <v>5</v>
       </c>
@@ -3685,7 +3667,7 @@
         <v>143</v>
       </c>
     </row>
-    <row r="140" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="140" spans="1:5">
       <c r="A140" t="s">
         <v>5</v>
       </c>
@@ -3702,7 +3684,7 @@
         <v>144</v>
       </c>
     </row>
-    <row r="141" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="141" spans="1:5">
       <c r="A141" t="s">
         <v>5</v>
       </c>
@@ -3719,7 +3701,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="142" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="142" spans="1:5">
       <c r="A142" t="s">
         <v>5</v>
       </c>
@@ -3736,7 +3718,7 @@
         <v>146</v>
       </c>
     </row>
-    <row r="143" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="143" spans="1:5">
       <c r="A143" t="s">
         <v>5</v>
       </c>
@@ -3753,7 +3735,7 @@
         <v>147</v>
       </c>
     </row>
-    <row r="144" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="144" spans="1:5">
       <c r="A144" t="s">
         <v>5</v>
       </c>
@@ -3770,7 +3752,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="145" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="145" spans="1:5">
       <c r="A145" t="s">
         <v>5</v>
       </c>
@@ -3787,7 +3769,7 @@
         <v>149</v>
       </c>
     </row>
-    <row r="146" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="146" spans="1:5">
       <c r="A146" t="s">
         <v>5</v>
       </c>
@@ -3804,7 +3786,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="147" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="147" spans="1:5">
       <c r="A147" t="s">
         <v>5</v>
       </c>
@@ -3821,7 +3803,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="148" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="148" spans="1:5">
       <c r="A148" t="s">
         <v>5</v>
       </c>
@@ -3838,7 +3820,7 @@
         <v>152</v>
       </c>
     </row>
-    <row r="149" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="149" spans="1:5">
       <c r="A149" t="s">
         <v>5</v>
       </c>
@@ -3855,7 +3837,7 @@
         <v>153</v>
       </c>
     </row>
-    <row r="150" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="150" spans="1:5">
       <c r="A150" t="s">
         <v>5</v>
       </c>
@@ -3872,7 +3854,7 @@
         <v>154</v>
       </c>
     </row>
-    <row r="151" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="151" spans="1:5">
       <c r="A151" t="s">
         <v>5</v>
       </c>
@@ -3889,7 +3871,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="152" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="152" spans="1:5">
       <c r="A152" t="s">
         <v>5</v>
       </c>
@@ -3906,7 +3888,7 @@
         <v>156</v>
       </c>
     </row>
-    <row r="153" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="153" spans="1:5">
       <c r="A153" t="s">
         <v>5</v>
       </c>
@@ -3923,7 +3905,7 @@
         <v>157</v>
       </c>
     </row>
-    <row r="154" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="154" spans="1:5">
       <c r="A154" t="s">
         <v>5</v>
       </c>
@@ -3940,7 +3922,7 @@
         <v>158</v>
       </c>
     </row>
-    <row r="155" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="155" spans="1:5">
       <c r="A155" t="s">
         <v>5</v>
       </c>
@@ -3951,13 +3933,13 @@
         <v>1970</v>
       </c>
       <c r="D155">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E155" t="s">
         <v>159</v>
       </c>
     </row>
-    <row r="156" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="156" spans="1:5">
       <c r="A156" t="s">
         <v>5</v>
       </c>
@@ -3974,7 +3956,7 @@
         <v>160</v>
       </c>
     </row>
-    <row r="157" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="157" spans="1:5">
       <c r="A157" t="s">
         <v>5</v>
       </c>
@@ -3991,7 +3973,7 @@
         <v>161</v>
       </c>
     </row>
-    <row r="158" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="158" spans="1:5">
       <c r="A158" t="s">
         <v>5</v>
       </c>
@@ -4008,7 +3990,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="159" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="159" spans="1:5">
       <c r="A159" t="s">
         <v>5</v>
       </c>
@@ -4025,7 +4007,7 @@
         <v>163</v>
       </c>
     </row>
-    <row r="160" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="160" spans="1:5">
       <c r="A160" t="s">
         <v>5</v>
       </c>
@@ -4042,7 +4024,7 @@
         <v>164</v>
       </c>
     </row>
-    <row r="161" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="161" spans="1:5">
       <c r="A161" t="s">
         <v>5</v>
       </c>
@@ -4059,7 +4041,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="162" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="162" spans="1:5">
       <c r="A162" t="s">
         <v>5</v>
       </c>
@@ -4076,7 +4058,7 @@
         <v>166</v>
       </c>
     </row>
-    <row r="163" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="163" spans="1:5">
       <c r="A163" t="s">
         <v>5</v>
       </c>
@@ -4093,7 +4075,7 @@
         <v>167</v>
       </c>
     </row>
-    <row r="164" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="164" spans="1:5">
       <c r="A164" t="s">
         <v>5</v>
       </c>
@@ -4110,7 +4092,7 @@
         <v>168</v>
       </c>
     </row>
-    <row r="165" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="165" spans="1:5">
       <c r="A165" t="s">
         <v>5</v>
       </c>
@@ -4127,7 +4109,7 @@
         <v>169</v>
       </c>
     </row>
-    <row r="166" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="166" spans="1:5">
       <c r="A166" t="s">
         <v>5</v>
       </c>
@@ -4144,7 +4126,7 @@
         <v>170</v>
       </c>
     </row>
-    <row r="167" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="167" spans="1:5">
       <c r="A167" t="s">
         <v>5</v>
       </c>
@@ -4161,7 +4143,7 @@
         <v>171</v>
       </c>
     </row>
-    <row r="168" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="168" spans="1:5">
       <c r="A168" t="s">
         <v>5</v>
       </c>
@@ -4178,7 +4160,7 @@
         <v>172</v>
       </c>
     </row>
-    <row r="169" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="169" spans="1:5">
       <c r="A169" t="s">
         <v>5</v>
       </c>
@@ -4195,7 +4177,7 @@
         <v>173</v>
       </c>
     </row>
-    <row r="170" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="170" spans="1:5">
       <c r="A170" t="s">
         <v>5</v>
       </c>
@@ -4212,7 +4194,7 @@
         <v>174</v>
       </c>
     </row>
-    <row r="171" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="171" spans="1:5">
       <c r="A171" t="s">
         <v>5</v>
       </c>
@@ -4229,7 +4211,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="172" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="172" spans="1:5">
       <c r="A172" t="s">
         <v>5</v>
       </c>
@@ -4246,7 +4228,7 @@
         <v>176</v>
       </c>
     </row>
-    <row r="173" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="173" spans="1:5">
       <c r="A173" t="s">
         <v>5</v>
       </c>
@@ -4263,7 +4245,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="174" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="174" spans="1:5">
       <c r="A174" t="s">
         <v>5</v>
       </c>
@@ -4280,7 +4262,7 @@
         <v>178</v>
       </c>
     </row>
-    <row r="175" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="175" spans="1:5">
       <c r="A175" t="s">
         <v>5</v>
       </c>
@@ -4297,7 +4279,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="176" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="176" spans="1:5">
       <c r="A176" t="s">
         <v>5</v>
       </c>
@@ -4314,7 +4296,7 @@
         <v>180</v>
       </c>
     </row>
-    <row r="177" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="177" spans="1:5">
       <c r="A177" t="s">
         <v>5</v>
       </c>
@@ -4331,7 +4313,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="178" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="178" spans="1:5">
       <c r="A178" t="s">
         <v>5</v>
       </c>
@@ -4348,7 +4330,7 @@
         <v>182</v>
       </c>
     </row>
-    <row r="179" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="179" spans="1:5">
       <c r="A179" t="s">
         <v>5</v>
       </c>
@@ -4365,7 +4347,7 @@
         <v>183</v>
       </c>
     </row>
-    <row r="180" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="180" spans="1:5">
       <c r="A180" t="s">
         <v>5</v>
       </c>
@@ -4382,7 +4364,7 @@
         <v>184</v>
       </c>
     </row>
-    <row r="181" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="181" spans="1:5">
       <c r="A181" t="s">
         <v>5</v>
       </c>
@@ -4399,7 +4381,7 @@
         <v>185</v>
       </c>
     </row>
-    <row r="182" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="182" spans="1:5">
       <c r="A182" t="s">
         <v>5</v>
       </c>
@@ -4416,7 +4398,7 @@
         <v>186</v>
       </c>
     </row>
-    <row r="183" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="183" spans="1:5">
       <c r="A183" t="s">
         <v>5</v>
       </c>
@@ -4433,7 +4415,7 @@
         <v>187</v>
       </c>
     </row>
-    <row r="184" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="184" spans="1:5">
       <c r="A184" t="s">
         <v>5</v>
       </c>
@@ -4450,7 +4432,7 @@
         <v>188</v>
       </c>
     </row>
-    <row r="185" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="185" spans="1:5">
       <c r="A185" t="s">
         <v>5</v>
       </c>
@@ -4467,7 +4449,7 @@
         <v>189</v>
       </c>
     </row>
-    <row r="186" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="186" spans="1:5">
       <c r="A186" t="s">
         <v>5</v>
       </c>
@@ -4484,7 +4466,7 @@
         <v>190</v>
       </c>
     </row>
-    <row r="187" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="187" spans="1:5">
       <c r="A187" t="s">
         <v>5</v>
       </c>
@@ -4501,7 +4483,7 @@
         <v>191</v>
       </c>
     </row>
-    <row r="188" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="188" spans="1:5">
       <c r="A188" t="s">
         <v>5</v>
       </c>
@@ -4518,7 +4500,7 @@
         <v>192</v>
       </c>
     </row>
-    <row r="189" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="189" spans="1:5">
       <c r="A189" t="s">
         <v>5</v>
       </c>
@@ -4535,7 +4517,7 @@
         <v>193</v>
       </c>
     </row>
-    <row r="190" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="190" spans="1:5">
       <c r="A190" t="s">
         <v>5</v>
       </c>
@@ -4552,7 +4534,7 @@
         <v>194</v>
       </c>
     </row>
-    <row r="191" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="191" spans="1:5">
       <c r="A191" t="s">
         <v>5</v>
       </c>
@@ -4569,7 +4551,7 @@
         <v>195</v>
       </c>
     </row>
-    <row r="192" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="192" spans="1:5">
       <c r="A192" t="s">
         <v>5</v>
       </c>
@@ -4586,7 +4568,7 @@
         <v>196</v>
       </c>
     </row>
-    <row r="193" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="193" spans="1:5">
       <c r="A193" t="s">
         <v>5</v>
       </c>
@@ -4603,7 +4585,7 @@
         <v>197</v>
       </c>
     </row>
-    <row r="194" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="194" spans="1:5">
       <c r="A194" t="s">
         <v>5</v>
       </c>
@@ -4620,7 +4602,7 @@
         <v>198</v>
       </c>
     </row>
-    <row r="195" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="195" spans="1:5">
       <c r="A195" t="s">
         <v>5</v>
       </c>
@@ -4637,7 +4619,7 @@
         <v>199</v>
       </c>
     </row>
-    <row r="196" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="196" spans="1:5">
       <c r="A196" t="s">
         <v>5</v>
       </c>
@@ -4654,7 +4636,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="197" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="197" spans="1:5">
       <c r="A197" t="s">
         <v>5</v>
       </c>
@@ -4671,7 +4653,7 @@
         <v>201</v>
       </c>
     </row>
-    <row r="198" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="198" spans="1:5">
       <c r="A198" t="s">
         <v>5</v>
       </c>
@@ -4688,7 +4670,7 @@
         <v>202</v>
       </c>
     </row>
-    <row r="199" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="199" spans="1:5">
       <c r="A199" t="s">
         <v>5</v>
       </c>
@@ -4705,7 +4687,7 @@
         <v>203</v>
       </c>
     </row>
-    <row r="200" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="200" spans="1:5">
       <c r="A200" t="s">
         <v>5</v>
       </c>
@@ -4722,7 +4704,7 @@
         <v>204</v>
       </c>
     </row>
-    <row r="201" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="201" spans="1:5">
       <c r="A201" t="s">
         <v>5</v>
       </c>
@@ -4739,7 +4721,7 @@
         <v>205</v>
       </c>
     </row>
-    <row r="202" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="202" spans="1:5">
       <c r="A202" t="s">
         <v>5</v>
       </c>
@@ -4756,7 +4738,7 @@
         <v>206</v>
       </c>
     </row>
-    <row r="203" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="203" spans="1:5">
       <c r="A203" t="s">
         <v>5</v>
       </c>
@@ -4773,7 +4755,7 @@
         <v>207</v>
       </c>
     </row>
-    <row r="204" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="204" spans="1:5">
       <c r="A204" t="s">
         <v>5</v>
       </c>
@@ -4790,7 +4772,7 @@
         <v>208</v>
       </c>
     </row>
-    <row r="205" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="205" spans="1:5">
       <c r="A205" t="s">
         <v>5</v>
       </c>
@@ -4807,7 +4789,7 @@
         <v>209</v>
       </c>
     </row>
-    <row r="206" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="206" spans="1:5">
       <c r="A206" t="s">
         <v>5</v>
       </c>
@@ -4824,7 +4806,7 @@
         <v>210</v>
       </c>
     </row>
-    <row r="207" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="207" spans="1:5">
       <c r="A207" t="s">
         <v>5</v>
       </c>
@@ -4841,7 +4823,7 @@
         <v>211</v>
       </c>
     </row>
-    <row r="208" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="208" spans="1:5">
       <c r="A208" t="s">
         <v>5</v>
       </c>
@@ -4858,7 +4840,7 @@
         <v>212</v>
       </c>
     </row>
-    <row r="209" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="209" spans="1:5">
       <c r="A209" t="s">
         <v>5</v>
       </c>
@@ -4875,7 +4857,7 @@
         <v>213</v>
       </c>
     </row>
-    <row r="210" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="210" spans="1:5">
       <c r="A210" t="s">
         <v>5</v>
       </c>
@@ -4892,7 +4874,7 @@
         <v>214</v>
       </c>
     </row>
-    <row r="211" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="211" spans="1:5">
       <c r="A211" t="s">
         <v>5</v>
       </c>
@@ -4909,7 +4891,7 @@
         <v>215</v>
       </c>
     </row>
-    <row r="212" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="212" spans="1:5">
       <c r="A212" t="s">
         <v>5</v>
       </c>
@@ -4926,7 +4908,7 @@
         <v>216</v>
       </c>
     </row>
-    <row r="213" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="213" spans="1:5">
       <c r="A213" t="s">
         <v>5</v>
       </c>
@@ -4943,7 +4925,7 @@
         <v>217</v>
       </c>
     </row>
-    <row r="214" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="214" spans="1:5">
       <c r="A214" t="s">
         <v>5</v>
       </c>
@@ -4960,7 +4942,7 @@
         <v>218</v>
       </c>
     </row>
-    <row r="215" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="215" spans="1:5">
       <c r="A215" t="s">
         <v>5</v>
       </c>
@@ -4977,7 +4959,7 @@
         <v>219</v>
       </c>
     </row>
-    <row r="216" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="216" spans="1:5">
       <c r="A216" t="s">
         <v>5</v>
       </c>
@@ -4994,7 +4976,7 @@
         <v>220</v>
       </c>
     </row>
-    <row r="217" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="217" spans="1:5">
       <c r="A217" t="s">
         <v>5</v>
       </c>
@@ -5011,7 +4993,7 @@
         <v>221</v>
       </c>
     </row>
-    <row r="218" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="218" spans="1:5">
       <c r="A218" t="s">
         <v>5</v>
       </c>
@@ -5028,7 +5010,7 @@
         <v>222</v>
       </c>
     </row>
-    <row r="219" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="219" spans="1:5">
       <c r="A219" t="s">
         <v>5</v>
       </c>
@@ -5045,7 +5027,7 @@
         <v>223</v>
       </c>
     </row>
-    <row r="220" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="220" spans="1:5">
       <c r="A220" t="s">
         <v>5</v>
       </c>
@@ -5062,7 +5044,7 @@
         <v>224</v>
       </c>
     </row>
-    <row r="221" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="221" spans="1:5">
       <c r="A221" t="s">
         <v>5</v>
       </c>
@@ -5079,7 +5061,7 @@
         <v>225</v>
       </c>
     </row>
-    <row r="222" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="222" spans="1:5">
       <c r="A222" t="s">
         <v>5</v>
       </c>
@@ -5096,7 +5078,7 @@
         <v>226</v>
       </c>
     </row>
-    <row r="223" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="223" spans="1:5">
       <c r="A223" t="s">
         <v>5</v>
       </c>
@@ -5113,7 +5095,7 @@
         <v>227</v>
       </c>
     </row>
-    <row r="224" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="224" spans="1:5">
       <c r="A224" t="s">
         <v>5</v>
       </c>
@@ -5130,7 +5112,7 @@
         <v>228</v>
       </c>
     </row>
-    <row r="225" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="225" spans="1:5">
       <c r="A225" t="s">
         <v>5</v>
       </c>
@@ -5147,7 +5129,7 @@
         <v>229</v>
       </c>
     </row>
-    <row r="226" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="226" spans="1:5">
       <c r="A226" t="s">
         <v>5</v>
       </c>
@@ -5164,7 +5146,7 @@
         <v>230</v>
       </c>
     </row>
-    <row r="227" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="227" spans="1:5">
       <c r="A227" t="s">
         <v>5</v>
       </c>
@@ -5181,7 +5163,7 @@
         <v>231</v>
       </c>
     </row>
-    <row r="228" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="228" spans="1:5">
       <c r="A228" t="s">
         <v>5</v>
       </c>
@@ -5198,7 +5180,7 @@
         <v>232</v>
       </c>
     </row>
-    <row r="229" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="229" spans="1:5">
       <c r="A229" t="s">
         <v>5</v>
       </c>
@@ -5209,13 +5191,13 @@
         <v>1970</v>
       </c>
       <c r="D229">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E229" t="s">
         <v>233</v>
       </c>
     </row>
-    <row r="230" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="230" spans="1:5">
       <c r="A230" t="s">
         <v>5</v>
       </c>
@@ -5232,7 +5214,7 @@
         <v>234</v>
       </c>
     </row>
-    <row r="231" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="231" spans="1:5">
       <c r="A231" t="s">
         <v>5</v>
       </c>
@@ -5249,7 +5231,7 @@
         <v>235</v>
       </c>
     </row>
-    <row r="232" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="232" spans="1:5">
       <c r="A232" t="s">
         <v>5</v>
       </c>
@@ -5266,7 +5248,7 @@
         <v>236</v>
       </c>
     </row>
-    <row r="233" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="233" spans="1:5">
       <c r="A233" t="s">
         <v>5</v>
       </c>
@@ -5283,7 +5265,7 @@
         <v>237</v>
       </c>
     </row>
-    <row r="234" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="234" spans="1:5">
       <c r="A234" t="s">
         <v>5</v>
       </c>
@@ -5300,7 +5282,7 @@
         <v>238</v>
       </c>
     </row>
-    <row r="235" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="235" spans="1:5">
       <c r="A235" t="s">
         <v>5</v>
       </c>
@@ -5317,7 +5299,7 @@
         <v>239</v>
       </c>
     </row>
-    <row r="236" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="236" spans="1:5">
       <c r="A236" t="s">
         <v>5</v>
       </c>
@@ -5334,7 +5316,7 @@
         <v>240</v>
       </c>
     </row>
-    <row r="237" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="237" spans="1:5">
       <c r="A237" t="s">
         <v>5</v>
       </c>
@@ -5351,7 +5333,7 @@
         <v>241</v>
       </c>
     </row>
-    <row r="238" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="238" spans="1:5">
       <c r="A238" t="s">
         <v>5</v>
       </c>
@@ -5368,7 +5350,7 @@
         <v>242</v>
       </c>
     </row>
-    <row r="239" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="239" spans="1:5">
       <c r="A239" t="s">
         <v>5</v>
       </c>
@@ -5379,13 +5361,13 @@
         <v>1970</v>
       </c>
       <c r="D239">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E239" t="s">
         <v>243</v>
       </c>
     </row>
-    <row r="240" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="240" spans="1:5">
       <c r="A240" t="s">
         <v>5</v>
       </c>
@@ -5402,7 +5384,7 @@
         <v>244</v>
       </c>
     </row>
-    <row r="241" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="241" spans="1:5">
       <c r="A241" t="s">
         <v>5</v>
       </c>
@@ -5419,7 +5401,7 @@
         <v>245</v>
       </c>
     </row>
-    <row r="242" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="242" spans="1:5">
       <c r="A242" t="s">
         <v>5</v>
       </c>
@@ -5436,7 +5418,7 @@
         <v>246</v>
       </c>
     </row>
-    <row r="243" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="243" spans="1:5">
       <c r="A243" t="s">
         <v>5</v>
       </c>
@@ -5453,7 +5435,7 @@
         <v>247</v>
       </c>
     </row>
-    <row r="244" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="244" spans="1:5">
       <c r="A244" t="s">
         <v>5</v>
       </c>
@@ -5470,7 +5452,7 @@
         <v>248</v>
       </c>
     </row>
-    <row r="245" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="245" spans="1:5">
       <c r="A245" t="s">
         <v>5</v>
       </c>
@@ -5481,13 +5463,13 @@
         <v>1970</v>
       </c>
       <c r="D245">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E245" t="s">
         <v>249</v>
       </c>
     </row>
-    <row r="246" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="246" spans="1:5">
       <c r="A246" t="s">
         <v>5</v>
       </c>
@@ -5504,7 +5486,7 @@
         <v>250</v>
       </c>
     </row>
-    <row r="247" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="247" spans="1:5">
       <c r="A247" t="s">
         <v>5</v>
       </c>
@@ -5521,7 +5503,7 @@
         <v>251</v>
       </c>
     </row>
-    <row r="248" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="248" spans="1:5">
       <c r="A248" t="s">
         <v>5</v>
       </c>
@@ -5532,13 +5514,13 @@
         <v>1970</v>
       </c>
       <c r="D248">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E248" t="s">
         <v>252</v>
       </c>
     </row>
-    <row r="249" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="249" spans="1:5">
       <c r="A249" t="s">
         <v>5</v>
       </c>
@@ -5555,7 +5537,7 @@
         <v>253</v>
       </c>
     </row>
-    <row r="250" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="250" spans="1:5">
       <c r="A250" t="s">
         <v>5</v>
       </c>
@@ -5566,13 +5548,13 @@
         <v>1970</v>
       </c>
       <c r="D250">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E250" t="s">
         <v>254</v>
       </c>
     </row>
-    <row r="251" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="251" spans="1:5">
       <c r="A251" t="s">
         <v>5</v>
       </c>
@@ -5583,13 +5565,13 @@
         <v>1970</v>
       </c>
       <c r="D251">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E251" t="s">
         <v>255</v>
       </c>
     </row>
-    <row r="252" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="252" spans="1:5">
       <c r="A252" t="s">
         <v>5</v>
       </c>
@@ -5606,7 +5588,7 @@
         <v>256</v>
       </c>
     </row>
-    <row r="253" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="253" spans="1:5">
       <c r="A253" t="s">
         <v>5</v>
       </c>
@@ -5623,7 +5605,7 @@
         <v>257</v>
       </c>
     </row>
-    <row r="254" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="254" spans="1:5">
       <c r="A254" t="s">
         <v>5</v>
       </c>
@@ -5640,7 +5622,7 @@
         <v>258</v>
       </c>
     </row>
-    <row r="255" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="255" spans="1:5">
       <c r="A255" t="s">
         <v>5</v>
       </c>
@@ -5657,7 +5639,7 @@
         <v>259</v>
       </c>
     </row>
-    <row r="256" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="256" spans="1:5">
       <c r="A256" t="s">
         <v>5</v>
       </c>
@@ -5668,13 +5650,13 @@
         <v>1970</v>
       </c>
       <c r="D256">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E256" t="s">
         <v>260</v>
       </c>
     </row>
-    <row r="257" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="257" spans="1:5">
       <c r="A257" t="s">
         <v>5</v>
       </c>
@@ -5691,7 +5673,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="258" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="258" spans="1:5">
       <c r="A258" t="s">
         <v>5</v>
       </c>
@@ -5708,7 +5690,7 @@
         <v>262</v>
       </c>
     </row>
-    <row r="259" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="259" spans="1:5">
       <c r="A259" t="s">
         <v>5</v>
       </c>
@@ -5725,7 +5707,7 @@
         <v>263</v>
       </c>
     </row>
-    <row r="260" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="260" spans="1:5">
       <c r="A260" t="s">
         <v>5</v>
       </c>
@@ -5736,13 +5718,13 @@
         <v>1970</v>
       </c>
       <c r="D260">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E260" t="s">
         <v>264</v>
       </c>
     </row>
-    <row r="261" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="261" spans="1:5">
       <c r="A261" t="s">
         <v>5</v>
       </c>
@@ -5759,7 +5741,7 @@
         <v>265</v>
       </c>
     </row>
-    <row r="262" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="262" spans="1:5">
       <c r="A262" t="s">
         <v>5</v>
       </c>
@@ -5776,7 +5758,7 @@
         <v>266</v>
       </c>
     </row>
-    <row r="263" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="263" spans="1:5">
       <c r="A263" t="s">
         <v>5</v>
       </c>
@@ -5793,7 +5775,7 @@
         <v>267</v>
       </c>
     </row>
-    <row r="264" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="264" spans="1:5">
       <c r="A264" t="s">
         <v>5</v>
       </c>
@@ -5810,7 +5792,7 @@
         <v>268</v>
       </c>
     </row>
-    <row r="265" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="265" spans="1:5">
       <c r="A265" t="s">
         <v>5</v>
       </c>
@@ -5827,7 +5809,7 @@
         <v>269</v>
       </c>
     </row>
-    <row r="266" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="266" spans="1:5">
       <c r="A266" t="s">
         <v>5</v>
       </c>
@@ -5844,7 +5826,7 @@
         <v>270</v>
       </c>
     </row>
-    <row r="267" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="267" spans="1:5">
       <c r="A267" t="s">
         <v>5</v>
       </c>
@@ -5861,7 +5843,7 @@
         <v>271</v>
       </c>
     </row>
-    <row r="268" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="268" spans="1:5">
       <c r="A268" t="s">
         <v>5</v>
       </c>
@@ -5878,7 +5860,7 @@
         <v>272</v>
       </c>
     </row>
-    <row r="269" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="269" spans="1:5">
       <c r="A269" t="s">
         <v>5</v>
       </c>
@@ -5895,7 +5877,7 @@
         <v>273</v>
       </c>
     </row>
-    <row r="270" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="270" spans="1:5">
       <c r="A270" t="s">
         <v>5</v>
       </c>
@@ -5912,7 +5894,7 @@
         <v>274</v>
       </c>
     </row>
-    <row r="271" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="271" spans="1:5">
       <c r="A271" t="s">
         <v>5</v>
       </c>
@@ -5929,7 +5911,7 @@
         <v>275</v>
       </c>
     </row>
-    <row r="272" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="272" spans="1:5">
       <c r="A272" t="s">
         <v>5</v>
       </c>
@@ -5946,7 +5928,7 @@
         <v>276</v>
       </c>
     </row>
-    <row r="273" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="273" spans="1:5">
       <c r="A273" t="s">
         <v>5</v>
       </c>
@@ -5963,7 +5945,7 @@
         <v>277</v>
       </c>
     </row>
-    <row r="274" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="274" spans="1:5">
       <c r="A274" t="s">
         <v>5</v>
       </c>
@@ -5980,7 +5962,7 @@
         <v>278</v>
       </c>
     </row>
-    <row r="275" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="275" spans="1:5">
       <c r="A275" t="s">
         <v>5</v>
       </c>
@@ -5997,7 +5979,7 @@
         <v>279</v>
       </c>
     </row>
-    <row r="276" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="276" spans="1:5">
       <c r="A276" t="s">
         <v>5</v>
       </c>
@@ -6014,7 +5996,7 @@
         <v>280</v>
       </c>
     </row>
-    <row r="277" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="277" spans="1:5">
       <c r="A277" t="s">
         <v>5</v>
       </c>
@@ -6031,7 +6013,7 @@
         <v>281</v>
       </c>
     </row>
-    <row r="278" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="278" spans="1:5">
       <c r="A278" t="s">
         <v>5</v>
       </c>
@@ -6048,7 +6030,7 @@
         <v>282</v>
       </c>
     </row>
-    <row r="279" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="279" spans="1:5">
       <c r="A279" t="s">
         <v>5</v>
       </c>
@@ -6065,7 +6047,7 @@
         <v>283</v>
       </c>
     </row>
-    <row r="280" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="280" spans="1:5">
       <c r="A280" t="s">
         <v>5</v>
       </c>
@@ -6082,7 +6064,7 @@
         <v>284</v>
       </c>
     </row>
-    <row r="281" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="281" spans="1:5">
       <c r="A281" t="s">
         <v>5</v>
       </c>
@@ -6099,7 +6081,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="282" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="282" spans="1:5">
       <c r="A282" t="s">
         <v>5</v>
       </c>
@@ -6116,7 +6098,7 @@
         <v>286</v>
       </c>
     </row>
-    <row r="283" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="283" spans="1:5">
       <c r="A283" t="s">
         <v>5</v>
       </c>
@@ -6133,7 +6115,7 @@
         <v>287</v>
       </c>
     </row>
-    <row r="284" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="284" spans="1:5">
       <c r="A284" t="s">
         <v>5</v>
       </c>
@@ -6150,7 +6132,7 @@
         <v>288</v>
       </c>
     </row>
-    <row r="285" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="285" spans="1:5">
       <c r="A285" t="s">
         <v>5</v>
       </c>
@@ -6167,7 +6149,7 @@
         <v>289</v>
       </c>
     </row>
-    <row r="286" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="286" spans="1:5">
       <c r="A286" t="s">
         <v>5</v>
       </c>
@@ -6184,7 +6166,7 @@
         <v>290</v>
       </c>
     </row>
-    <row r="287" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="287" spans="1:5">
       <c r="A287" t="s">
         <v>5</v>
       </c>
@@ -6201,7 +6183,7 @@
         <v>291</v>
       </c>
     </row>
-    <row r="288" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="288" spans="1:5">
       <c r="A288" t="s">
         <v>5</v>
       </c>
@@ -6218,7 +6200,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="289" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="289" spans="1:5">
       <c r="A289" t="s">
         <v>5</v>
       </c>
@@ -6235,7 +6217,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="290" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="290" spans="1:5">
       <c r="A290" t="s">
         <v>5</v>
       </c>
@@ -6252,7 +6234,7 @@
         <v>294</v>
       </c>
     </row>
-    <row r="291" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="291" spans="1:5">
       <c r="A291" t="s">
         <v>5</v>
       </c>
@@ -6269,7 +6251,7 @@
         <v>295</v>
       </c>
     </row>
-    <row r="292" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="292" spans="1:5">
       <c r="A292" t="s">
         <v>5</v>
       </c>
@@ -6280,13 +6262,13 @@
         <v>1970</v>
       </c>
       <c r="D292">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E292" t="s">
         <v>296</v>
       </c>
     </row>
-    <row r="293" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="293" spans="1:5">
       <c r="A293" t="s">
         <v>5</v>
       </c>
@@ -6303,7 +6285,7 @@
         <v>297</v>
       </c>
     </row>
-    <row r="294" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="294" spans="1:5">
       <c r="A294" t="s">
         <v>5</v>
       </c>
@@ -6320,7 +6302,7 @@
         <v>298</v>
       </c>
     </row>
-    <row r="295" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="295" spans="1:5">
       <c r="A295" t="s">
         <v>5</v>
       </c>
@@ -6337,7 +6319,7 @@
         <v>299</v>
       </c>
     </row>
-    <row r="296" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="296" spans="1:5">
       <c r="A296" t="s">
         <v>5</v>
       </c>
@@ -6354,7 +6336,7 @@
         <v>300</v>
       </c>
     </row>
-    <row r="297" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="297" spans="1:5">
       <c r="A297" t="s">
         <v>5</v>
       </c>
@@ -6371,7 +6353,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="298" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="298" spans="1:5">
       <c r="A298" t="s">
         <v>5</v>
       </c>
@@ -6388,7 +6370,7 @@
         <v>302</v>
       </c>
     </row>
-    <row r="299" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="299" spans="1:5">
       <c r="A299" t="s">
         <v>5</v>
       </c>
@@ -6405,7 +6387,7 @@
         <v>303</v>
       </c>
     </row>
-    <row r="300" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="300" spans="1:5">
       <c r="A300" t="s">
         <v>5</v>
       </c>
@@ -6422,7 +6404,7 @@
         <v>304</v>
       </c>
     </row>
-    <row r="301" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="301" spans="1:5">
       <c r="A301" t="s">
         <v>5</v>
       </c>
@@ -6439,7 +6421,7 @@
         <v>305</v>
       </c>
     </row>
-    <row r="302" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="302" spans="1:5">
       <c r="A302" t="s">
         <v>5</v>
       </c>
@@ -6456,7 +6438,7 @@
         <v>306</v>
       </c>
     </row>
-    <row r="303" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="303" spans="1:5">
       <c r="A303" t="s">
         <v>5</v>
       </c>
@@ -6473,7 +6455,7 @@
         <v>307</v>
       </c>
     </row>
-    <row r="304" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="304" spans="1:5">
       <c r="A304" t="s">
         <v>5</v>
       </c>
@@ -6490,7 +6472,7 @@
         <v>308</v>
       </c>
     </row>
-    <row r="305" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="305" spans="1:5">
       <c r="A305" t="s">
         <v>5</v>
       </c>
@@ -6508,6 +6490,6 @@
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>